--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,19 +539,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>h_01KFN5VN33W6V4TKMMX55CFV6R</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFN5VN33W6V4TKMMX55CFV6R</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Configuration - Update all links</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Features List</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,63 +583,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01K3TMW0YGBNCAV57V69WX0VWV</t>
+          <t>h_01KMMA69K704VGB3TJEGRDBT26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3TMW0YGBNCAV57V69WX0VWV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMMA69K704VGB3TJEGRDBT26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>h_01KPT1K2EXVBPTARSTCZ39ZR8F</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPT1K2EXVBPTARSTCZ39ZR8F</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,41 +649,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Execution Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manage Expense</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Manage Expense</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,85 +715,85 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>User Creation Notifications</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>User Creation Notifications</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,63 +847,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01KEVE7XCZQH52141730TYQVCA</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,32 +935,54 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Run Integration</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Features List</t>
+          <t>Feature List Copy / Features List</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>UKG Ready</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,19 +605,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KPT1K2EXVBPTARSTCZ39ZR8F</t>
+          <t>h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPT1K2EXVBPTARSTCZ39ZR8F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,63 +627,63 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>h_01KPT689W1C92MCJG3WTWJ784Y</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPT689W1C92MCJG3WTWJ784Y</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Manage Expense</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,41 +693,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Manage Expense</t>
+          <t>User Creation Notifications</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>User Creation Notifications</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,41 +759,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,85 +825,85 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KEVE7XCZQH52141730TYQVCA</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,76 +913,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Run Integration</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Run Integration</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Time Based Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,41 +649,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>h_01KPTE79E0VXGWZ4A2NXGQB7BY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTE79E0VXGWZ4A2NXGQB7BY</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manage Expense</t>
+          <t>SAP Concur</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>h_01KPTG3TT263211BEKW68BDE7S</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTG3TT263211BEKW68BDE7S</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Target Application Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,41 +693,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>h_01KPTG08Q8SE8KYQX39464196J</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTG08Q8SE8KYQX39464196J</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>User Creation Notifications</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Manage Expense</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,41 +737,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>User Creation Notifications</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,41 +781,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,120 +825,186 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KEVE7XCZQH52141730TYQVCA</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Entitlements</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Run Integration</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KPTG3TT263211BEKW68BDE7S</t>
+          <t>h_01KPTHNYJQWMVWGGD8H26EKNCS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTG3TT263211BEKW68BDE7S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTHNYJQWMVWGGD8H26EKNCS</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Manage Employee</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,41 +715,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>h_01KPTHNYJQ2MCC91C249B8KB2W</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTHNYJQ2MCC91C249B8KB2W</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Manage Expense</t>
+          <t>Employee Correlation Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>h_01KPTGTG5SH4Y5FEFD6HD60NZT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTGTG5SH4Y5FEFD6HD60NZT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,41 +759,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>User Creation Notifications</t>
+          <t>Manage Expense</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>User Creation Notifications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,41 +825,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,85 +891,85 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01KEVE7XCZQH52141730TYQVCA</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,32 +979,76 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Run Integration</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -671,12 +671,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KPTHNYJQWMVWGGD8H26EKNCS</t>
+          <t>h_01KPTS2MXC1S0PDZGG12EE3ZAS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTHNYJQWMVWGGD8H26EKNCS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTS2MXC1S0PDZGG12EE3ZAS</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KPTHNYJQ2MCC91C249B8KB2W</t>
+          <t>h_01KPTS2MXCS05V9577BPCRBKXF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTHNYJQ2MCC91C249B8KB2W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTS2MXCS05V9577BPCRBKXF</t>
         </is>
       </c>
     </row>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,51 +749,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Safeguard Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>h_01KPX2KZ7TYZRD16NY15A9PEW4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX2KZ7TYZRD16NY15A9PEW4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Manage Expense</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>h_01KPX5G7H1XVKGM0E697NYH5GD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX5G7H1XVKGM0E697NYH5GD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,41 +803,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>User Creation Notifications</t>
+          <t>Manage Expense</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>User Creation Notifications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,41 +869,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,85 +935,85 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01KEVE7XCZQH52141730TYQVCA</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,32 +1023,76 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Run Integration</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Employee Creation Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,107 +781,107 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KPX5G7H1XVKGM0E697NYH5GD</t>
+          <t>h_01KPX5WSFGJHFC8R1JNMTGM5Y3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX5G7H1XVKGM0E697NYH5GD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX5WSFGJHFC8R1JNMTGM5Y3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Employee Update Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>h_01KPZ9HQFP0SVK6QFYVC8C9EQB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPZ9HQFP0SVK6QFYVC8C9EQB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Manage Expense</t>
+          <t>Employee Termination Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>h_01KPZ9HQFPNNCADD9AC4FCVTVW</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPZ9HQFPNNCADD9AC4FCVTVW</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>h_01KPX5G7H1XVKGM0E697NYH5GD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX5G7H1XVKGM0E697NYH5GD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>User Creation Notifications</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Manage Expense</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>User Creation Notifications</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,41 +935,41 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,120 +979,186 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01KEVE7XCZQH52141730TYQVCA</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Entitlements</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Run Integration</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -859,7 +859,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Manage Expense</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Manage Expense</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,85 +891,85 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>User Creation Notifications</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>User Creation Notifications</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,63 +1023,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01KEVE7XCZQH52141730TYQVCA</t>
+          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,54 +1111,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Run Integration</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Run Integration</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,51 +881,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>User Creation Notifications</t>
+          <t>Business Groups</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Access Rules</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,63 +935,63 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Retention Rules</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01KMQNB8YF19XTGQXY5SNGKXZJ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQNB8YF19XTGQXY5SNGKXZJ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Monitoring Rules</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Monitoring Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Rule Detail (Monitoring)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,41 +1023,41 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01KEVE7XCZQH52141730TYQVCA</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVE7XCZQH52141730TYQVCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,54 +1089,208 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>User Creation Notifications</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Operational Settings</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Debug Settings</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Entitlements</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Run Integration</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Feature List Copy / Features List</t>
+          <t>Feature List</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Time Based Settings</t>
+          <t>Time-Based Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Manage Employee</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Employee Correlation Settings</t>
+          <t>Employee Match Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -837,29 +837,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KPX5G7H1XVKGM0E697NYH5GD</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX5G7H1XVKGM0E697NYH5GD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Manage Expense</t>
+          <t>Monitoring Rules</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,129 +869,129 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KDDAV3EAHNZE8QK11E0YJGYB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Monitoring Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Business Groups</t>
+          <t>Rule Detail (Monitoring)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
+          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Access Rules</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Retention Rules</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KMQNB8YF19XTGQXY5SNGKXZJ</t>
+          <t>h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQNB8YF19XTGQXY5SNGKXZJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Monitoring Rules</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Monitoring Settings</t>
+          <t>User Creation Notifications</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,107 +1001,107 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
+          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rule Detail (Monitoring)</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>User Creation Notifications</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,186 +1111,76 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Run Integration</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Log Settings</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Report Settings</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Entitlements</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Run Integration</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>DRAFT version</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -463,29 +463,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Key Functions</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01KD80JD2B42MPX32NQSRYS5EN</t>
+          <t>h_01KR0XZXSHKRPJC7M3R57VMSZJ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KD80JD2B42MPX32NQSRYS5EN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KR0XZXSHKRPJC7M3R57VMSZJ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Key Functions</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,63 +495,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01KD80KT84CHY25GM05997PQ8Q</t>
+          <t>h_01KD80JD2B42MPX32NQSRYS5EN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KD80KT84CHY25GM05997PQ8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KD80JD2B42MPX32NQSRYS5EN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>h_01KD80KT84CHY25GM05997PQ8Q</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KD80KT84CHY25GM05997PQ8Q</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01KFN5VN33W6V4TKMMX55CFV6R</t>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFN5VN33W6V4TKMMX55CFV6R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,85 +561,85 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
+          <t>h_01KFN5VN33W6V4TKMMX55CFV6R</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFN5VN33W6V4TKMMX55CFV6R</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Feature List</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KMMA69K704VGB3TJEGRDBT26</t>
+          <t>h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMMA69K704VGB3TJEGRDBT26</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UKG Ready</t>
+          <t>Feature List</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
+          <t>h_01KMMA69K704VGB3TJEGRDBT26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMMA69K704VGB3TJEGRDBT26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>UKG Ready</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KPT689W1C92MCJG3WTWJ784Y</t>
+          <t>h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPT689W1C92MCJG3WTWJ784Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Time-Based Settings</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,63 +649,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KPTE79E0VXGWZ4A2NXGQB7BY</t>
+          <t>h_01KPT689W1C92MCJG3WTWJ784Y</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTE79E0VXGWZ4A2NXGQB7BY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPT689W1C92MCJG3WTWJ784Y</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SAP Concur</t>
+          <t>Time-Based Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KPTS2MXC1S0PDZGG12EE3ZAS</t>
+          <t>h_01KPTE79E0VXGWZ4A2NXGQB7BY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTS2MXC1S0PDZGG12EE3ZAS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTE79E0VXGWZ4A2NXGQB7BY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Target Application Settings</t>
+          <t>SAP Concur</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KPTG08Q8SE8KYQX39464196J</t>
+          <t>h_01KPTS2MXC1S0PDZGG12EE3ZAS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTG08Q8SE8KYQX39464196J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTS2MXC1S0PDZGG12EE3ZAS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Target Application Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,41 +715,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KPTS2MXCS05V9577BPCRBKXF</t>
+          <t>h_01KPTG08Q8SE8KYQX39464196J</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTS2MXCS05V9577BPCRBKXF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTG08Q8SE8KYQX39464196J</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Employee Match Settings</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KPTGTG5SH4Y5FEFD6HD60NZT</t>
+          <t>h_01KPTS2MXCS05V9577BPCRBKXF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTGTG5SH4Y5FEFD6HD60NZT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTS2MXCS05V9577BPCRBKXF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Safeguard Settings</t>
+          <t>Employee Match Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KPX2KZ7TYZRD16NY15A9PEW4</t>
+          <t>h_01KPTGTG5SH4Y5FEFD6HD60NZT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX2KZ7TYZRD16NY15A9PEW4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTGTG5SH4Y5FEFD6HD60NZT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Employee Creation Settings</t>
+          <t>Safeguard Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KPX5WSFGJHFC8R1JNMTGM5Y3</t>
+          <t>h_01KPX2KZ7TYZRD16NY15A9PEW4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX5WSFGJHFC8R1JNMTGM5Y3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX2KZ7TYZRD16NY15A9PEW4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Employee Update Settings</t>
+          <t>Employee Creation Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KPZ9HQFP0SVK6QFYVC8C9EQB</t>
+          <t>h_01KPX5WSFGJHFC8R1JNMTGM5Y3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPZ9HQFP0SVK6QFYVC8C9EQB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX5WSFGJHFC8R1JNMTGM5Y3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Employee Termination Settings</t>
+          <t>Employee Update Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,85 +825,85 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KPZ9HQFPNNCADD9AC4FCVTVW</t>
+          <t>h_01KPZ9HQFP0SVK6QFYVC8C9EQB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPZ9HQFPNNCADD9AC4FCVTVW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPZ9HQFP0SVK6QFYVC8C9EQB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Employee Termination Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KPZ9HQFPNNCADD9AC4FCVTVW</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPZ9HQFPNNCADD9AC4FCVTVW</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Monitoring Rules</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Monitoring Settings</t>
+          <t>Monitoring Rules</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
+          <t>h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rule Detail (Monitoring)</t>
+          <t>Monitoring Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
+          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Rule Detail (Monitoring)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,85 +979,85 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>User Creation Notifications</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>User Creation Notifications</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,34 +1111,34 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFJRNFACHS8WM9P5V7MT582D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DRAFT version</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,41 +451,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>h_01KD7Y3KD9MT7413QHSHAVZCNF</t>
+          <t>h_01KR0XZXSHKRPJC7M3R57VMSZJ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KD7Y3KD9MT7413QHSHAVZCNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KR0XZXSHKRPJC7M3R57VMSZJ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Key Functions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01KR0XZXSHKRPJC7M3R57VMSZJ</t>
+          <t>h_01KD80JD2B42MPX32NQSRYS5EN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KR0XZXSHKRPJC7M3R57VMSZJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KD80JD2B42MPX32NQSRYS5EN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Key Functions</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,63 +495,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01KD80JD2B42MPX32NQSRYS5EN</t>
+          <t>h_01KD80KT84CHY25GM05997PQ8Q</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KD80JD2B42MPX32NQSRYS5EN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KD80KT84CHY25GM05997PQ8Q</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01KD80KT84CHY25GM05997PQ8Q</t>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KD80KT84CHY25GM05997PQ8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>h_01KFN5VN33W6V4TKMMX55CFV6R</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFN5VN33W6V4TKMMX55CFV6R</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,107 +561,107 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01KFN5VN33W6V4TKMMX55CFV6R</t>
+          <t>h_01KRGRBX8VDAJKQK6WVRMWZ6KF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFN5VN33W6V4TKMMX55CFV6R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KRGRBX8VDAJKQK6WVRMWZ6KF</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
+          <t>h_01KRGR79ZPSPJ54EWVS60HHBAR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KRGR79ZPSPJ54EWVS60HHBAR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Feature List</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KMMA69K704VGB3TJEGRDBT26</t>
+          <t>h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMMA69K704VGB3TJEGRDBT26</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UKG Ready</t>
+          <t>Feature List</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
+          <t>h_01KMMA69K704VGB3TJEGRDBT26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMMA69K704VGB3TJEGRDBT26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>UKG Ready</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KPT689W1C92MCJG3WTWJ784Y</t>
+          <t>h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPT689W1C92MCJG3WTWJ784Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Time-Based Settings</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,63 +671,63 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KPTE79E0VXGWZ4A2NXGQB7BY</t>
+          <t>h_01KPT689W1C92MCJG3WTWJ784Y</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTE79E0VXGWZ4A2NXGQB7BY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPT689W1C92MCJG3WTWJ784Y</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAP Concur</t>
+          <t>Time-Based Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KPTS2MXC1S0PDZGG12EE3ZAS</t>
+          <t>h_01KPTE79E0VXGWZ4A2NXGQB7BY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTS2MXC1S0PDZGG12EE3ZAS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTE79E0VXGWZ4A2NXGQB7BY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Target Application Settings</t>
+          <t>SAP Concur</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KPTG08Q8SE8KYQX39464196J</t>
+          <t>h_01KPTS2MXC1S0PDZGG12EE3ZAS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTG08Q8SE8KYQX39464196J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTS2MXC1S0PDZGG12EE3ZAS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Target Application Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,41 +737,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KPTS2MXCS05V9577BPCRBKXF</t>
+          <t>h_01KPTG08Q8SE8KYQX39464196J</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTS2MXCS05V9577BPCRBKXF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTG08Q8SE8KYQX39464196J</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Employee Match Settings</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KPTGTG5SH4Y5FEFD6HD60NZT</t>
+          <t>h_01KPTS2MXCS05V9577BPCRBKXF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTGTG5SH4Y5FEFD6HD60NZT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPTS2MXCS05V9577BPCRBKXF</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Safeguard Settings</t>
+          <t>Employee Creation Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KPX2KZ7TYZRD16NY15A9PEW4</t>
+          <t>h_01KPX5WSFGJHFC8R1JNMTGM5Y3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX2KZ7TYZRD16NY15A9PEW4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX5WSFGJHFC8R1JNMTGM5Y3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Employee Creation Settings</t>
+          <t>Employee Update Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KPX5WSFGJHFC8R1JNMTGM5Y3</t>
+          <t>h_01KPZ9HQFP0SVK6QFYVC8C9EQB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPX5WSFGJHFC8R1JNMTGM5Y3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPZ9HQFP0SVK6QFYVC8C9EQB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Employee Update Settings</t>
+          <t>Employee Termination Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,85 +825,85 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KPZ9HQFP0SVK6QFYVC8C9EQB</t>
+          <t>h_01KPZ9HQFPNNCADD9AC4FCVTVW</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPZ9HQFP0SVK6QFYVC8C9EQB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPZ9HQFPNNCADD9AC4FCVTVW</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Employee Termination Settings</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KPZ9HQFPNNCADD9AC4FCVTVW</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KPZ9HQFPNNCADD9AC4FCVTVW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Monitoring Rules</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Monitoring Rules</t>
+          <t>Monitoring Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
+          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Monitoring Settings</t>
+          <t>Rule Detail (Monitoring)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
+          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rule Detail (Monitoring)</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,63 +957,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
+          <t>h_01KRJT84K90M1Y60B3NB68QGKQ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KRJT84K90M1Y60B3NB68QGKQ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>User Creation Notifications</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,166 +1023,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NRMYBN1KPWF14T49Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KRJTWD4BYN1ZC8MK3323BRTC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KRJTWD4BYN1ZC8MK3323BRTC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Run Integration</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>

--- a/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/SAP-Concur-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,73 +837,73 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Manage Expenses</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KRN63BENH3VDCQRPNEGC7EWB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KRN63BENH3VDCQRPNEGC7EWB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Monitoring Rules</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Monitoring Settings</t>
+          <t>Monitoring Rules</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
+          <t>h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70PP7YV5EME6BDSSVYYCWT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rule Detail (Monitoring)</t>
+          <t>Monitoring Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
+          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Rule Detail (Monitoring)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,41 +957,41 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KRJT84K90M1Y60B3NB68QGKQ</t>
+          <t>h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KRJT84K90M1Y60B3NB68QGKQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KQ70J6NZ69D87F1XJ89PFX5G</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>h_01KRJT84K90M1Y60B3NB68QGKQ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KRJT84K90M1Y60B3NB68QGKQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#01KEVCPV02BP8SAN60Y62Q2F7A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,120 +1045,142 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KRJTWD4BYN1ZC8MK3323BRTC</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KRJTWD4BYN1ZC8MK3323BRTC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KRJTWD4BYN1ZC8MK3323BRTC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01KRJTWD4BYN1ZC8MK3323BRTC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SAP-Concur-UKG-Ready-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
